--- a/WS-TP10.xlsx
+++ b/WS-TP10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanni\Documents\Mines de Paris\1A\MPI\TP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yanni\Documents\Mines de Paris\1A\MPI\rapport-TP-MPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85454E2-2D67-4309-8557-C10B0C878B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF8DE8D-AED3-4F32-AF33-F69F31880380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -606,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -693,24 +693,21 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -729,24 +726,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -839,16 +835,6 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
-            <c:dLbl>
-              <c:idx val="273"/>
-              <c:delete val="1"/>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-6E55-4403-B3DB-D20ECD847FAD}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
             <c:dLbl>
               <c:idx val="274"/>
               <c:showLegendKey val="0"/>
@@ -5880,304 +5866,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="B1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="35.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="2:4" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="41" t="s">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="C7" s="6">
         <v>13</v>
       </c>
-      <c r="C7" s="6">
+      <c r="D7" s="6">
         <v>12.4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="41"/>
-      <c r="B8" s="6">
-        <v>12.4</v>
-      </c>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="60"/>
       <c r="C8" s="6">
         <v>12.4</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="41"/>
-      <c r="B9" s="6">
+      <c r="D8" s="6">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="60"/>
+      <c r="C9" s="6">
         <v>12.2</v>
       </c>
-      <c r="C9" s="6">
+      <c r="D9" s="6">
         <v>11.9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="41"/>
-      <c r="B10" s="6">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="60"/>
+      <c r="C10" s="6">
         <v>12.4</v>
       </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="41"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="41"/>
-      <c r="B12" s="7" t="s">
+      <c r="D10" s="6"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="60"/>
+      <c r="C11" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="41"/>
-      <c r="B13" s="7">
-        <f xml:space="preserve"> AVERAGEA(B7:B10)</f>
+    <row r="12" spans="2:4" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="60"/>
+      <c r="C12" s="7">
+        <f xml:space="preserve"> AVERAGEA(C7:C10)</f>
         <v>12.499999999999998</v>
       </c>
-      <c r="C13" s="7">
-        <f xml:space="preserve"> AVERAGEA(C7:C10)</f>
+      <c r="D12" s="7">
+        <f xml:space="preserve"> AVERAGEA(D7:D10)</f>
         <v>12.233333333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="41" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="6">
+      <c r="C13" s="6">
         <v>12.1</v>
       </c>
+      <c r="D13" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="60"/>
       <c r="C14" s="6">
+        <v>12.6</v>
+      </c>
+      <c r="D14" s="6">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="60"/>
+      <c r="C15" s="6">
+        <v>11.2</v>
+      </c>
+      <c r="D15" s="6">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B16" s="60"/>
+      <c r="C16" s="6">
+        <v>10.9</v>
+      </c>
+      <c r="D16" s="6"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="60"/>
+      <c r="C17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="60"/>
+      <c r="C18" s="7">
+        <f xml:space="preserve"> AVERAGEA(C13:C16)</f>
+        <v>11.7</v>
+      </c>
+      <c r="D18" s="7">
+        <f xml:space="preserve"> AVERAGEA(D13:D16)</f>
+        <v>11.933333333333332</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="6">
+        <v>12.7</v>
+      </c>
+      <c r="D19" s="6">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="60"/>
+      <c r="C20" s="6">
+        <v>12.9</v>
+      </c>
+      <c r="D20" s="6">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="41"/>
-      <c r="B15" s="6">
-        <v>12.6</v>
-      </c>
-      <c r="C15" s="6">
-        <v>12.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="41"/>
-      <c r="B16" s="6">
-        <v>11.2</v>
-      </c>
-      <c r="C16" s="6">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="41"/>
-      <c r="B17" s="6">
-        <v>10.9</v>
-      </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="41"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="41"/>
-      <c r="B19" s="7" t="s">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="60"/>
+      <c r="C21" s="6">
+        <v>13</v>
+      </c>
+      <c r="D21" s="6">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="60"/>
+      <c r="C22" s="6">
+        <v>13.1</v>
+      </c>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="60"/>
+      <c r="C23" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="41"/>
-      <c r="B20" s="7">
-        <f xml:space="preserve"> AVERAGEA(B14:B17)</f>
-        <v>11.7</v>
-      </c>
-      <c r="C20" s="7">
-        <f xml:space="preserve"> AVERAGEA(C14:C17)</f>
-        <v>11.933333333333332</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="6">
-        <v>12.7</v>
-      </c>
-      <c r="C21" s="6">
-        <v>12.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="41"/>
-      <c r="B22" s="6">
-        <v>12.9</v>
-      </c>
-      <c r="C22" s="6">
+    <row r="24" spans="2:4" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="60"/>
+      <c r="C24" s="7">
+        <f xml:space="preserve"> AVERAGEA(C19:C22)</f>
+        <v>12.925000000000001</v>
+      </c>
+      <c r="D24" s="7">
+        <f xml:space="preserve"> AVERAGEA(D19:D22)</f>
+        <v>12.200000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="62" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="41"/>
-      <c r="B23" s="6">
+      <c r="D26" s="62"/>
+    </row>
+    <row r="27" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="62"/>
+    </row>
+    <row r="28" spans="2:4" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="6">
-        <v>12.1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="41"/>
-      <c r="B24" s="6">
-        <v>13.1</v>
-      </c>
-      <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="41"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="41"/>
-      <c r="B26" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" s="8" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="41"/>
-      <c r="B27" s="7">
-        <f xml:space="preserve"> AVERAGEA(B21:B24)</f>
-        <v>12.925000000000001</v>
-      </c>
-      <c r="C27" s="7">
-        <f xml:space="preserve"> AVERAGEA(C21:C24)</f>
-        <v>12.200000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="40"/>
-    </row>
-    <row r="30" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C30" s="40"/>
-    </row>
-    <row r="31" spans="1:3" ht="28.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="43" t="s">
+      <c r="C28" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="43"/>
-    </row>
-    <row r="32" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="40" t="s">
+      <c r="D28" s="59"/>
+    </row>
+    <row r="29" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="62" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="40"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+      <c r="D29" s="62"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="C30" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="40"/>
-    </row>
-    <row r="34" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="43" t="s">
+      <c r="D30" s="62"/>
+    </row>
+    <row r="31" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="43"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="D31" s="59"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
         <v>18</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="C32" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="C35" s="40"/>
-    </row>
-    <row r="36" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="43" t="s">
+      <c r="D32" s="62"/>
+    </row>
+    <row r="33" spans="3:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="43"/>
+      <c r="D33" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="B19:B24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -6194,11 +6165,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -6220,37 +6191,37 @@
       <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="40"/>
+      <c r="C6" s="62"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="40"/>
+      <c r="C7" s="62"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="40"/>
+      <c r="C8" s="62"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="40"/>
+      <c r="C9" s="62"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
@@ -6260,14 +6231,14 @@
       <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="40"/>
+      <c r="C11" s="62"/>
     </row>
     <row r="12" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6317,10 +6288,10 @@
       <c r="F1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J1" s="44"/>
+      <c r="J1" s="63"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
@@ -12798,14 +12769,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="61" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -12827,13 +12798,13 @@
       <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
@@ -13443,8 +13414,8 @@
       <c r="Q30" s="24"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
       <c r="D31" s="9"/>
       <c r="E31" s="23" t="s">
         <v>55</v>
@@ -13475,8 +13446,8 @@
       <c r="Q32" s="24"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
       <c r="D33" s="9"/>
       <c r="L33" s="24"/>
       <c r="M33" s="24"/>
@@ -13488,13 +13459,13 @@
       <c r="A34" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="40" t="s">
+      <c r="B34" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
       <c r="L34" s="24"/>
       <c r="M34" s="24"/>
       <c r="O34" s="24"/>
@@ -13502,11 +13473,11 @@
       <c r="Q34" s="24"/>
     </row>
     <row r="35" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
       <c r="L35" s="24"/>
       <c r="M35" s="24"/>
       <c r="O35" s="24"/>
@@ -13517,13 +13488,13 @@
       <c r="A36" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B36" s="43" t="s">
+      <c r="B36" s="59" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-      <c r="F36" s="40"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="62"/>
       <c r="L36" s="24"/>
       <c r="M36" s="24"/>
       <c r="O36" s="24"/>
@@ -13531,13 +13502,13 @@
       <c r="Q36" s="24"/>
     </row>
     <row r="37" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="43" t="s">
+      <c r="B37" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
       <c r="L37" s="24"/>
       <c r="M37" s="24"/>
       <c r="O37" s="24"/>
@@ -13548,13 +13519,13 @@
       <c r="A38" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="40" t="s">
+      <c r="B38" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="40"/>
-      <c r="D38" s="40"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="40"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
       <c r="L38" s="24"/>
       <c r="M38" s="24"/>
       <c r="O38" s="24"/>
@@ -13562,13 +13533,13 @@
       <c r="Q38" s="24"/>
     </row>
     <row r="39" spans="1:17" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="43" t="s">
+      <c r="B39" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
       <c r="L39" s="24"/>
       <c r="M39" s="24"/>
       <c r="O39" s="24"/>
@@ -13579,13 +13550,13 @@
       <c r="A40" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="62" t="s">
         <v>75</v>
       </c>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
       <c r="L40" s="24"/>
       <c r="M40" s="24"/>
       <c r="O40" s="24"/>
@@ -25587,88 +25558,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
       <c r="K1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="46"/>
       <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
       <c r="B3" s="35"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="36"/>
       <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="31"/>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="52"/>
       <c r="K4" s="33"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="32"/>
       <c r="B5" s="35"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="36"/>
       <c r="K5" s="33"/>
     </row>
     <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="32"/>
       <c r="B6" s="35"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="36"/>
       <c r="K6" s="33"/>
     </row>
@@ -25676,57 +25647,57 @@
       <c r="A7" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="61"/>
-      <c r="I7" s="61"/>
-      <c r="J7" s="62"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="46"/>
       <c r="K7" s="33"/>
     </row>
     <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="32"/>
       <c r="B8" s="35"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="63"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="63"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="36"/>
       <c r="K8" s="33"/>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="31"/>
-      <c r="B9" s="49" t="s">
+      <c r="B9" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
-      <c r="J9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="33"/>
     </row>
     <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="32"/>
       <c r="B10" s="35"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
-      <c r="G10" s="63"/>
-      <c r="H10" s="63"/>
-      <c r="I10" s="63"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="36"/>
       <c r="K10" s="33"/>
     </row>
@@ -25734,45 +25705,45 @@
       <c r="A11" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="46"/>
       <c r="K11" s="33"/>
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="32"/>
       <c r="B12" s="35"/>
-      <c r="C12" s="63"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="63"/>
-      <c r="F12" s="63"/>
-      <c r="G12" s="63"/>
-      <c r="H12" s="63"/>
-      <c r="I12" s="63"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
       <c r="J12" s="36"/>
       <c r="K12" s="33"/>
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="32"/>
-      <c r="B13" s="52" t="s">
+      <c r="B13" s="53" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="54"/>
+      <c r="G13" s="54"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="54"/>
+      <c r="J13" s="55"/>
       <c r="K13" s="33"/>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -25790,75 +25761,75 @@
     </row>
     <row r="15" spans="1:11" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="32"/>
-      <c r="B15" s="55" t="s">
+      <c r="B15" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="56"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="56"/>
-      <c r="J15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="58"/>
       <c r="K15" s="34"/>
     </row>
     <row r="16" spans="1:11" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="32"/>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="41"/>
       <c r="K16" s="34"/>
     </row>
     <row r="17" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
-      <c r="F17" s="61"/>
-      <c r="G17" s="61"/>
-      <c r="H17" s="61"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="62"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="46"/>
       <c r="K17" s="33"/>
     </row>
     <row r="18" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="14"/>
       <c r="B18" s="35"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="36"/>
       <c r="K18" s="33"/>
     </row>
     <row r="19" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="14"/>
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="53" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="54"/>
+      <c r="G19" s="54"/>
+      <c r="H19" s="54"/>
+      <c r="I19" s="54"/>
+      <c r="J19" s="55"/>
       <c r="K19" s="33"/>
     </row>
     <row r="20" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -25876,17 +25847,17 @@
     </row>
     <row r="21" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
-      <c r="B21" s="52" t="s">
+      <c r="B21" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="54"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="55"/>
       <c r="K21" s="33"/>
     </row>
     <row r="22" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -25904,17 +25875,17 @@
     </row>
     <row r="23" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="28"/>
-      <c r="B23" s="55" t="s">
+      <c r="B23" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="58"/>
       <c r="K23" s="34"/>
     </row>
     <row r="24" spans="1:11" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -25934,26 +25905,21 @@
       <c r="A25" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="48"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="49"/>
       <c r="K25" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B7:J7"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B17:J17"/>
     <mergeCell ref="B25:J25"/>
     <mergeCell ref="B4:J4"/>
     <mergeCell ref="B9:J9"/>
@@ -25962,6 +25928,11 @@
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B21:J21"/>
     <mergeCell ref="B23:J23"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B17:J17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
